--- a/docs/sample-transcript/학급-전과목-성적-샘플.xlsx
+++ b/docs/sample-transcript/학급-전과목-성적-샘플.xlsx
@@ -43,7 +43,7 @@
     <t>성명</t>
   </si>
   <si>
-    <t>원점수</t>
+    <t>원점수/과목평균(표준편차)</t>
   </si>
   <si>
     <t>성취도(수강자수)</t>
